--- a/output/pdf_financials_xlsx/RRM.H.xlsx
+++ b/output/pdf_financials_xlsx/RRM.H.xlsx
@@ -4687,37 +4687,37 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.20039</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.20039</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.20039</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.20039</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.20039</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.20039</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.20039</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.20039</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.20039</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.20039</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.20039</v>
       </c>
       <c r="M92" s="1" t="inlineStr">
         <is>
@@ -7396,7 +7396,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -8504,7 +8508,11 @@
           <t>Reserves 2,200,390</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -9650,7 +9658,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>2.20039</v>
       </c>

--- a/output/pdf_financials_xlsx/RRM.H.xlsx
+++ b/output/pdf_financials_xlsx/RRM.H.xlsx
@@ -1967,37 +1967,37 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>6.999999999999999e-05</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.000129</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.0009990000000000001</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.000289</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.013006</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.000732</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.011135</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.005337</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.002137</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.000925</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.000853</v>
       </c>
       <c r="M34" s="1" t="inlineStr">
         <is>
@@ -2057,37 +2057,37 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>6.999999999999999e-05</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.000129</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.0009990000000000001</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.000289</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.013006</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.000732</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.011135</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.005337</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.002137</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.000925</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.000853</v>
       </c>
       <c r="M36" s="1" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -14572,7 +14572,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -15924,7 +15924,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">

--- a/output/pdf_financials_xlsx/RRM.H.xlsx
+++ b/output/pdf_financials_xlsx/RRM.H.xlsx
@@ -3383,16 +3383,16 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.183482</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.153694</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.138148</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.054793</v>
       </c>
       <c r="F64" s="3" t="n">
         <v>0</v>
@@ -3518,16 +3518,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.0063</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.0063</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="F67" s="3" t="n">
         <v>0</v>
@@ -5084,7 +5084,7 @@
         <v>-0.001546</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001452</v>
       </c>
       <c r="M101" s="1" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>-0.00613</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0.029282</v>
+        <v>0.02783</v>
       </c>
       <c r="M106" s="1" t="inlineStr">
         <is>
@@ -10474,7 +10474,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -11900,7 +11904,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
